--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104518_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104518_W7.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2148</v>
+        <v>8.4702</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9212</v>
+        <v>7.6478</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2936</v>
+        <v>0.8224</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9587</v>
+        <v>6.9428</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7303</v>
+        <v>4.7113</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2284</v>
+        <v>2.2316</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4645</v>
+        <v>7.4251</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6684</v>
+        <v>4.64</v>
       </c>
       <c r="L2" t="n">
-        <v>2.796</v>
+        <v>2.7851</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5057</v>
+        <v>-0.4822</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8951</v>
+        <v>1.1616</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4384</v>
+        <v>0.9388</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1636</v>
+        <v>5.8759</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0603</v>
+        <v>3.9949</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1034</v>
+        <v>1.8811</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5919</v>
+        <v>5.2557</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3391</v>
+        <v>4.4005</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2529</v>
+        <v>0.8551</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0209</v>
+        <v>5.0497</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7895</v>
+        <v>4.1713</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2315</v>
+        <v>0.8783</v>
       </c>
       <c r="M3" t="n">
-        <v>0.571</v>
+        <v>0.206</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5496</v>
+        <v>0.2292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0214</v>
+        <v>-0.0232</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9838</v>
+        <v>0.165</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9467</v>
+        <v>0.0834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0372</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.791</v>
+        <v>4.3276</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2511</v>
+        <v>3.2897</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5399</v>
+        <v>1.0379</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2628</v>
+        <v>2.6005</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4098</v>
+        <v>1.3384</v>
       </c>
       <c r="I4" t="n">
-        <v>0.853</v>
+        <v>1.2621</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0808</v>
+        <v>2.0077</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1906</v>
+        <v>0.7789</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8902</v>
+        <v>1.2288</v>
       </c>
       <c r="M4" t="n">
-        <v>0.182</v>
+        <v>0.5928</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2192</v>
+        <v>0.5595</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0372</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9255</v>
+        <v>0.1337</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>0.1925</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2299</v>
+        <v>-0.0589</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9792</v>
+        <v>2.7989</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5044</v>
+        <v>2.1712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4748</v>
+        <v>0.6277</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4091</v>
+        <v>2.3979</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4966</v>
+        <v>3.479</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0875</v>
+        <v>-1.0812</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8162</v>
+        <v>2.7787</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1201</v>
+        <v>3.0919</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4071</v>
+        <v>-0.3808</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1615</v>
+        <v>-0.3227</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3176</v>
+        <v>0.0346</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4791</v>
+        <v>-0.3573</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4928</v>
+        <v>0.9583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4309</v>
+        <v>1.8959</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0619</v>
+        <v>-0.9376</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2054</v>
+        <v>0.1977</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0476</v>
+        <v>1.3789</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8423</v>
+        <v>-1.1813</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1912</v>
+        <v>-0.2083</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2685</v>
+        <v>1.0062</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-1.2146</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9858</v>
+        <v>0.406</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2209</v>
+        <v>0.3727</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>0.0333</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6484</v>
+        <v>-0.3077</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5081</v>
+        <v>-0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1403</v>
+        <v>-0.0752</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4417</v>
+        <v>0.1261</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6303</v>
+        <v>0.1735</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1885</v>
+        <v>-0.0474</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2045</v>
+        <v>1.2039</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3853</v>
+        <v>2.0423</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1808</v>
+        <v>-0.8385</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1775</v>
+        <v>2.1759</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0248</v>
+        <v>2.258</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2023</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.382</v>
+        <v>-0.972</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3605</v>
+        <v>-0.2157</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0214</v>
+        <v>-0.7563</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8308</v>
+        <v>0.2881</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>0.2739</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2925</v>
+        <v>0.0141</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2066</v>
+        <v>-0.2611</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6344</v>
+        <v>-0.093</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.841</v>
+        <v>-0.1681</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2687</v>
+        <v>-1.1915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5545</v>
+        <v>-1.1454</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2605</v>
+        <v>-0.0487</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5888</v>
+        <v>0.2273</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6717</v>
+        <v>-0.276</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008200000000000001</v>
+        <v>-1.1428</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1255</v>
+        <v>-0.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>-0.8694</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2979</v>
+        <v>0.2475</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5081</v>
+        <v>-0.0444</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2102</v>
+        <v>0.2919</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4119</v>
+        <v>-0.2687</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5001</v>
+        <v>1.634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0882</v>
+        <v>-1.9028</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1979</v>
+        <v>2.5501</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0491</v>
+        <v>2.6452</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1488</v>
+        <v>-0.0951</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0313</v>
+        <v>3.0047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2353</v>
+        <v>2.6028</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2666</v>
+        <v>0.4019</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1666</v>
+        <v>-0.4546</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2844</v>
+        <v>0.0424</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8822</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1055</v>
+        <v>-0.4122</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.2325</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5743</v>
+        <v>-0.1797</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.741</v>
+        <v>-0.4478</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3501</v>
+        <v>0.2249</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0911</v>
+        <v>-0.6727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5437</v>
+        <v>1.2723</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6449</v>
+        <v>0.7151</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1012</v>
+        <v>0.5572</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0226</v>
+        <v>1.2563</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6148</v>
+        <v>0.5861</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4078</v>
+        <v>0.6703</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4789</v>
+        <v>0.016</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0301</v>
+        <v>0.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.509</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8726</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5383</v>
+        <v>0.1067</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3342</v>
+        <v>-0.0545</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.546</v>
+        <v>-2.2181</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3165</v>
+        <v>-1.2332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7705</v>
+        <v>-0.9849</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6411</v>
+        <v>-0.3357</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7228</v>
+        <v>-0.4281</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3639</v>
+        <v>0.0924</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5513</v>
+        <v>0.1349</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5195</v>
+        <v>-0.3415</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.0708</v>
+        <v>0.4764</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0898</v>
+        <v>-0.4706</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2033</v>
+        <v>-0.0866</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2931</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1051</v>
+        <v>-0.1312</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.1813</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.34</v>
+        <v>0.0501</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7448</v>
+        <v>-2.2303</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5163</v>
+        <v>-2.839</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2285</v>
+        <v>0.6087</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3409</v>
+        <v>-2.6348</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4315</v>
+        <v>0.7319</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0906</v>
+        <v>-3.3667</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1463</v>
+        <v>-2.567</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3361</v>
+        <v>0.5171</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4824</v>
+        <v>-3.0841</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4871</v>
+        <v>-0.0678</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0954</v>
+        <v>0.2148</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3918</v>
+        <v>-0.2826</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6554</v>
+        <v>-0.8035</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4869</v>
+        <v>-0.272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1685</v>
+        <v>-0.5315</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4328</v>
+        <v>17.131</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4498</v>
+        <v>16.8667</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0167999999999997</v>
+        <v>0.2642999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>18.2649</v>
+        <v>18.2589</v>
       </c>
       <c r="H13" t="n">
-        <v>21.01</v>
+        <v>20.9684</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7451</v>
+        <v>-2.7098</v>
       </c>
       <c r="J13" t="n">
-        <v>21.2429</v>
+        <v>21.009</v>
       </c>
       <c r="K13" t="n">
-        <v>19.6842</v>
+        <v>19.5381</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5587</v>
+        <v>1.4708</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9778</v>
+        <v>-2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3258</v>
+        <v>1.4303</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.3037</v>
+        <v>-4.1804</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6202000000000003</v>
+        <v>0.07090000000000007</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7559</v>
+        <v>-0.04880000000000004</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1357999999999998</v>
+        <v>0.1194000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.345999999999999</v>
+        <v>-2.3367</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1705</v>
+        <v>6.1499</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.516400000000001</v>
+        <v>-8.486499999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0512</v>
+        <v>2.0662</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5908</v>
+        <v>2.6781</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5396</v>
+        <v>-0.6119</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7678</v>
+        <v>0.7675</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4877</v>
+        <v>-0.4882</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2555</v>
+        <v>1.2558</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2353</v>
+        <v>2.2158</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1185</v>
+        <v>1.1064</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4675</v>
+        <v>-1.4483</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2214</v>
+        <v>-0.1974</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2474</v>
+        <v>0.1535</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0727</v>
+        <v>0.3381</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6774</v>
+        <v>0.8923</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6047</v>
+        <v>-0.5543</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0483</v>
+        <v>0.049</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.7239</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7756</v>
+        <v>0.773</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6841</v>
+        <v>1.6685</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6357</v>
+        <v>-1.6194</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3632</v>
+        <v>-0.0964</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1939</v>
+        <v>-1.0619</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1065</v>
+        <v>0.1447</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3004</v>
+        <v>-1.2066</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9609</v>
+        <v>-0.9922</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2265</v>
+        <v>-0.3544</v>
       </c>
       <c r="J16" t="n">
-        <v>1.647</v>
+        <v>0.1262</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4231</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2239</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6079</v>
+        <v>-1.1184</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1575</v>
+        <v>-0.6895</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4504</v>
+        <v>-0.4289</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>2.128</v>
+        <v>-0.2973</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5425</v>
+        <v>0.0185</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5855</v>
+        <v>-0.3159</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-1.3198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0323</v>
+        <v>1.1322</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-2.452</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4806</v>
+        <v>-0.955</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1096</v>
+        <v>-0.7379</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6291</v>
+        <v>-0.2171</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7571</v>
+        <v>1.6261</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5034</v>
+        <v>1.4027</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7463</v>
+        <v>0.2234</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7234</v>
+        <v>-2.5811</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6062</v>
+        <v>-2.1406</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1172</v>
+        <v>-0.4405</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7466</v>
+        <v>1.0009</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2431</v>
+        <v>0.6034</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5036</v>
+        <v>0.3975</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0674</v>
+        <v>-1.4361</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1447</v>
+        <v>-1.6075</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2122</v>
+        <v>0.1713</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9979</v>
+        <v>-2.2272</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6407</v>
+        <v>-2.3209</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3572</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1266</v>
+        <v>-0.8803</v>
       </c>
       <c r="K18" t="n">
-        <v>0.052</v>
+        <v>-1.2001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.3198</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1245</v>
+        <v>-1.3469</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6927</v>
+        <v>-1.1209</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2964</v>
+        <v>0.1568</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0181</v>
+        <v>-0.2232</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3145</v>
+        <v>0.3801</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.75</v>
+        <v>-1.5174</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0521</v>
+        <v>-0.6822</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3021</v>
+        <v>-0.8351</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2302</v>
+        <v>-2.4733</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3261</v>
+        <v>-3.105</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0959</v>
+        <v>0.6317</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8613</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1917</v>
+        <v>-1.5103</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3304</v>
+        <v>0.7447</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3689</v>
+        <v>-1.7077</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1344</v>
+        <v>-1.5946</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1588</v>
+        <v>0.886</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6956</v>
+        <v>0.5386</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3474</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2345</v>
+        <v>-1.7701</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0815</v>
+        <v>1.6821</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.153</v>
+        <v>-3.4522</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0947</v>
+        <v>-0.2099</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8631</v>
+        <v>-2.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2316</v>
+        <v>1.9479</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3477</v>
+        <v>2.2842</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1212</v>
+        <v>0.1551</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4689</v>
+        <v>2.1291</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.747</v>
+        <v>-2.4941</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9843</v>
+        <v>-2.313</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2373</v>
+        <v>-0.1811</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0472</v>
+        <v>-0.6284</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2662</v>
+        <v>-0.4835</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3133</v>
+        <v>-0.1449</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7479</v>
+        <v>-1.9988</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2461</v>
+        <v>-1.2193</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.994</v>
+        <v>-0.7795</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2157</v>
+        <v>-3.0904</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1748</v>
+        <v>-1.8476</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9591</v>
+        <v>-1.2428</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3094</v>
+        <v>-1.3699</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1559</v>
+        <v>0.1207</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1535</v>
+        <v>-1.4906</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5251</v>
+        <v>-1.7205</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3307</v>
+        <v>-1.9683</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1945</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6002</v>
+        <v>0.1811</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9557</v>
+        <v>0.1506</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6445</v>
+        <v>0.0305</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9192</v>
+        <v>-2.7242</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5099</v>
+        <v>-1.7045</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4291</v>
+        <v>-1.0197</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3918</v>
+        <v>-3.5139</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6191</v>
+        <v>-3.8504</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7727</v>
+        <v>0.3364</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3389</v>
+        <v>-1.1328</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3565</v>
+        <v>-1.2215</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6955</v>
+        <v>0.0887</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0529</v>
+        <v>-2.3811</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.9756</v>
+        <v>-2.6288</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0772</v>
+        <v>0.2477</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7921</v>
+        <v>0.1555</v>
       </c>
       <c r="T22" t="n">
-        <v>0.983</v>
+        <v>-0.2954</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1909</v>
+        <v>0.4509</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4434</v>
+        <v>-2.7773</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2362</v>
+        <v>-1.3467</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2072</v>
+        <v>-1.4306</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4896</v>
+        <v>-1.2127</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.8307</v>
+        <v>-2.4877</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3411</v>
+        <v>1.275</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0817</v>
+        <v>0.3515</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1855</v>
+        <v>-0.7207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1038</v>
+        <v>1.0722</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4079</v>
+        <v>-1.5642</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.6452</v>
+        <v>-1.767</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2373</v>
+        <v>0.2028</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5928</v>
+        <v>-0.0199</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8861</v>
+        <v>-0.1048</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2934</v>
+        <v>0.0849</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5327</v>
+        <v>-3.443</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9211</v>
+        <v>-0.2335</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6117</v>
+        <v>-3.2095</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2197</v>
+        <v>-4.4009</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4965</v>
+        <v>-2.6112</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2768</v>
+        <v>-1.7898</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3624</v>
+        <v>-1.3737</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7171</v>
+        <v>0.348</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0795</v>
+        <v>-1.7217</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5821</v>
+        <v>-3.0273</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7794</v>
+        <v>-2.9591</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1973</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7667</v>
+        <v>0.275</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6956</v>
+        <v>0.2783</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0711</v>
+        <v>-0.0033</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.4329</v>
+        <v>-15.6443</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01679999999999993</v>
+        <v>-0.2642999999999995</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.4499</v>
+        <v>-15.3801</v>
       </c>
       <c r="G25" t="n">
-        <v>-18.265</v>
+        <v>-18.259</v>
       </c>
       <c r="H25" t="n">
-        <v>-21.01</v>
+        <v>-20.9685</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7451</v>
+        <v>2.7094</v>
       </c>
       <c r="J25" t="n">
-        <v>2.978100000000001</v>
+        <v>2.75</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3257</v>
+        <v>-1.4303</v>
       </c>
       <c r="L25" t="n">
-        <v>4.3036</v>
+        <v>4.180299999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-21.2429</v>
+        <v>-21.009</v>
       </c>
       <c r="N25" t="n">
-        <v>-19.6843</v>
+        <v>-19.5381</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5586</v>
+        <v>-1.4709</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1344</v>
+        <v>-1.1384</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6200000000000002</v>
+        <v>1.4159</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1358</v>
+        <v>-0.1195</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7561000000000002</v>
+        <v>1.5353</v>
       </c>
       <c r="V25" t="n">
-        <v>2.346</v>
+        <v>2.3367</v>
       </c>
       <c r="W25" t="n">
-        <v>8.516499999999999</v>
+        <v>8.486600000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.1704</v>
+        <v>-6.149900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104518_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104518_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.486499999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104518_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.149900000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
